--- a/healthcare_surveys/013_radiotherapy_virtual_assistant_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/013_radiotherapy_virtual_assistant_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'once_a_day'}</t>
+          <t>once_a_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Once a day'}</t>
+          <t>Once a day</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'a_few_times_a_week'}</t>
+          <t>a_few_times_a_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'A few times a week'}</t>
+          <t>A few times a week</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'providing_information_on_available_treatment_options'}</t>
+          <t>providing_information_on_available_treatment_options</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Providing information on available treatment options'}</t>
+          <t>Providing information on available treatment options</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'suggesting_treatment_options_based_on_your_medical_history'}</t>
+          <t>suggesting_treatment_options_based_on_your_medical_history</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Suggesting treatment options based on your medical history'}</t>
+          <t>Suggesting treatment options based on your medical history</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'offering_appointment_reminders_and_scheduling'}</t>
+          <t>offering_appointment_reminders_and_scheduling</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Offering appointment reminders and scheduling'}</t>
+          <t>Offering appointment reminders and scheduling</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very likely'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'extremely_likely'}</t>
+          <t>extremely_likely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Extremely likely'}</t>
+          <t>Extremely likely</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'yes,_with_technical_issues'}</t>
+          <t>yes,_with_technical_issues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Yes, with technical issues'}</t>
+          <t>Yes, with technical issues</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'yes,_with_content_issues'}</t>
+          <t>yes,_with_content_issues</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Yes, with content issues'}</t>
+          <t>Yes, with content issues</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'desktop_or_laptop'}</t>
+          <t>desktop_or_laptop</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Desktop or laptop'}</t>
+          <t>Desktop or laptop</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'through_a_web_browser'}</t>
+          <t>through_a_web_browser</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Through a web browser'}</t>
+          <t>Through a web browser</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'through_an_app'}</t>
+          <t>through_an_app</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Through an app'}</t>
+          <t>Through an app</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
